--- a/src/attributions/attributions_saliency_traj_475.xlsx
+++ b/src/attributions/attributions_saliency_traj_475.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG6"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.04063398391008377</v>
+        <v>0.01304338499903679</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2720329165458679</v>
+        <v>1.176119089126587</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0120363924652338</v>
+        <v>0.2086013853549957</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1907553374767303</v>
+        <v>1.320990562438965</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0210262406617403</v>
+        <v>0.001341760158538818</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05467768758535385</v>
+        <v>0.6242766976356506</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01887047290802002</v>
+        <v>0.6200017929077148</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01561510190367699</v>
+        <v>0.3296214640140533</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03237568587064743</v>
+        <v>0.4592230319976807</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0135467667132616</v>
+        <v>0.1313447207212448</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2126912921667099</v>
+        <v>1.348271369934082</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001657273736782372</v>
+        <v>0.2235509753227234</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1834313422441483</v>
+        <v>1.726253032684326</v>
       </c>
       <c r="N2" t="n">
-        <v>0.006145946681499481</v>
+        <v>0.02568265423178673</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04768660292029381</v>
+        <v>0.4855125248432159</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02627939730882645</v>
+        <v>0.5483139753341675</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0297958217561245</v>
+        <v>0.2059715986251831</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05194133892655373</v>
+        <v>0.1369407176971436</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02295565418899059</v>
+        <v>0.0046472093090415</v>
       </c>
       <c r="T2" t="n">
-        <v>0.02906900085508823</v>
+        <v>0.1205405071377754</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01588838174939156</v>
+        <v>0.04121385887265205</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03240291401743889</v>
+        <v>0.1988110989332199</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02477239817380905</v>
+        <v>0.1931976675987244</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01319135911762714</v>
+        <v>0.6758183836936951</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.59750434756279e-05</v>
+        <v>0.009843881241977215</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03494727239012718</v>
+        <v>0.03158606588840485</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.02388528920710087</v>
+        <v>0.3827969431877136</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.02954559214413166</v>
+        <v>0.07231391966342926</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.01950367540121078</v>
+        <v>0.01097700744867325</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.04129014536738396</v>
+        <v>0.04933510720729828</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.04982651770114899</v>
+        <v>0.516190767288208</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.005672691389918327</v>
+        <v>0.3930315375328064</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.006808394566178322</v>
+        <v>0.1528273671865463</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.006502826698124409</v>
+        <v>0.2539302706718445</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.002117200754582882</v>
+        <v>0.05103050544857979</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.02420458011329174</v>
+        <v>0.1699684858322144</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.02070245891809464</v>
+        <v>0.03053071163594723</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.03455498814582825</v>
+        <v>0.2267428189516068</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001620778697542846</v>
+        <v>0.06179357692599297</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.005737773142755032</v>
+        <v>0.2766962051391602</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.009408026002347469</v>
+        <v>0.431953638792038</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0347914807498455</v>
+        <v>0.3565285205841064</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.00170697458088398</v>
+        <v>0.2664739489555359</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.03503211215138435</v>
+        <v>0.155816376209259</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.02594561502337456</v>
+        <v>0.08314669132232666</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.04034737125039101</v>
+        <v>0.009083880111575127</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1303691416978836</v>
+        <v>0.7878444194793701</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.01901711523532867</v>
+        <v>0.1678569167852402</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.04474128782749176</v>
+        <v>0.991841197013855</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.005811723414808512</v>
+        <v>0.133385181427002</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.03069213405251503</v>
+        <v>0.004281508736312389</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.01054367236793041</v>
+        <v>0.06721354275941849</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.0140625536441803</v>
+        <v>0.1518608331680298</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.04442118108272552</v>
+        <v>0.06225121021270752</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.009737381711602211</v>
+        <v>0.2022146731615067</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.06686101853847504</v>
+        <v>0.126115620136261</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.04503318294882774</v>
+        <v>0.3435353934764862</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.06866787374019623</v>
+        <v>0.1914275735616684</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03900749981403351</v>
+        <v>0.04558247327804565</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0138341411948204</v>
+        <v>0.464956521987915</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.02417772449553013</v>
+        <v>0.09581732004880905</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.03664616867899895</v>
+        <v>0.199375331401825</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.003106387797743082</v>
+        <v>0.6015268564224243</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.009682542644441128</v>
+        <v>0.02689173817634583</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01113706454634666</v>
+        <v>0.2285489141941071</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.01740868762135506</v>
+        <v>0.02075964212417603</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.02273097261786461</v>
+        <v>0.05496394634246826</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.001268882071599364</v>
+        <v>0.03403442353010178</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.02114028856158257</v>
+        <v>0.07286570221185684</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.01077981386333704</v>
+        <v>0.2520022690296173</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.01703479886054993</v>
+        <v>0.1818216443061829</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.003342777024954557</v>
+        <v>0.07616735994815826</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.05103498697280884</v>
+        <v>0.04367956519126892</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.08527769893407822</v>
+        <v>0.5601277351379395</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.007050018757581711</v>
+        <v>0.04123389348387718</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.04275121912360191</v>
+        <v>0.8226905465126038</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.02238464914262295</v>
+        <v>0.07683807611465454</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.00364276091568172</v>
+        <v>0.4495255053043365</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.005394597537815571</v>
+        <v>0.02222927659749985</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.02224613353610039</v>
+        <v>0.1197541952133179</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.05306262895464897</v>
+        <v>0.4439153969287872</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.008359930478036404</v>
+        <v>0.0006048192735761404</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.03975807875394821</v>
+        <v>0.3563310503959656</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.01762940734624863</v>
+        <v>0.1456993371248245</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.03796540945768356</v>
+        <v>0.4850134551525116</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01347165927290916</v>
+        <v>0.1278754025697708</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.003293827408924699</v>
+        <v>0.08075872808694839</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.01696336269378662</v>
+        <v>0.08090157061815262</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.002671456430107355</v>
+        <v>0.1749505996704102</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.007665775250643492</v>
+        <v>0.1443904787302017</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.01068473793566227</v>
+        <v>0.09388075768947601</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.007592132780700922</v>
+        <v>0.2278048694133759</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.01623550616204739</v>
+        <v>0.3571562767028809</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.003018924035131931</v>
+        <v>0.870405375957489</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.01209649629890919</v>
+        <v>0.2508500218391418</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.02687214873731136</v>
+        <v>0.0512901246547699</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.0255215410143137</v>
+        <v>0.1965912878513336</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.04868197068572044</v>
+        <v>0.2427444458007812</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.001368809025734663</v>
+        <v>0.4900879859924316</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.006170898675918579</v>
+        <v>0.04849234223365784</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04222424328327179</v>
+        <v>0.3636980056762695</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.02531462907791138</v>
+        <v>0.1093635857105255</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.04041473194956779</v>
+        <v>0.5260302424430847</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01361879985779524</v>
+        <v>0.07496181130409241</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0031289285980165</v>
+        <v>0.06363660097122192</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.01765650510787964</v>
+        <v>0.1301234662532806</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.00941130518913269</v>
+        <v>0.1451803892850876</v>
       </c>
       <c r="DD2" t="n">
-        <v>9.054807014763355e-05</v>
+        <v>0.1511578857898712</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.001402202993631363</v>
+        <v>0.1531775295734406</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1151817515492439</v>
+        <v>0.2510717809200287</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.01244277227669954</v>
+        <v>0.09664496034383774</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1230624318122864</v>
+        <v>0.2815041840076447</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.01790238358080387</v>
+        <v>0.04342339560389519</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.03090018220245838</v>
+        <v>0.005618506111204624</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.01672975346446037</v>
+        <v>0.007276646792888641</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.004980567842721939</v>
+        <v>0.7660614252090454</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.004164095968008041</v>
+        <v>0.09439417719841003</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.02155549079179764</v>
+        <v>0.02190125919878483</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.01918176375329494</v>
+        <v>0.06639096140861511</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.009807961992919445</v>
+        <v>0.09274853765964508</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.04490130022168159</v>
+        <v>0.3209809362888336</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.03712354600429535</v>
+        <v>0.06092397123575211</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.02123700454831123</v>
+        <v>0.01339810620993376</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.0102867791429162</v>
+        <v>0.172729104757309</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.002494809916242957</v>
+        <v>0.1896240413188934</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.02088282257318497</v>
+        <v>0.599604070186615</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.001864029327407479</v>
+        <v>0.1241684257984161</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.02326014265418053</v>
+        <v>0.08448924124240875</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.00142244016751647</v>
+        <v>0.1197453737258911</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.04109659790992737</v>
+        <v>0.05524633079767227</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0197511687874794</v>
+        <v>0.0417516753077507</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.0343717448413372</v>
+        <v>0.08052963763475418</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.01049619354307652</v>
+        <v>0.06925146281719208</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.02434039302170277</v>
+        <v>0.7075073719024658</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.008560116402804852</v>
+        <v>0.3974612057209015</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.0017560861306265</v>
+        <v>0.1300370544195175</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.02896792255342007</v>
+        <v>0.3159037828445435</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.02252776548266411</v>
+        <v>0.02018840052187443</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.003117703832685947</v>
+        <v>0.4234972894191742</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.01450694724917412</v>
+        <v>0.1613312661647797</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.0007363744080066681</v>
+        <v>0.1452113687992096</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.001299597439356148</v>
+        <v>0.1160983219742775</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.0006567547097802162</v>
+        <v>0.1296445429325104</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.001203052466735244</v>
+        <v>0.1281964480876923</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.003961788490414619</v>
+        <v>0.06931214779615402</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.0164056196808815</v>
+        <v>0.3170990943908691</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.04002569243311882</v>
+        <v>0.1133347675204277</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.0292637050151825</v>
+        <v>0.3036515414714813</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.01581955142319202</v>
+        <v>0.09403607994318008</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.06838132441043854</v>
+        <v>0.07672861218452454</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.03484438359737396</v>
+        <v>0.2847923934459686</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.0144999036565423</v>
+        <v>0.2149823904037476</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.01626945659518242</v>
+        <v>0.4067589938640594</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.005533690564334393</v>
+        <v>0.00504280487075448</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04230513051152229</v>
+        <v>0.3954823911190033</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.0212835781276226</v>
+        <v>0.1128553971648216</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.03875569999217987</v>
+        <v>0.6005354523658752</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01569040678441525</v>
+        <v>0.1245296970009804</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.001212530885823071</v>
+        <v>0.00282908882945776</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.02790526673197746</v>
+        <v>0.1361235678195953</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.01259704120457172</v>
+        <v>0.2549380958080292</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.009682719595730305</v>
+        <v>0.1519631594419479</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.005534756928682327</v>
+        <v>0.1024125516414642</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.02211732417345047</v>
+        <v>0.2063370496034622</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.01257309690117836</v>
+        <v>0.1643902659416199</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.006784954108297825</v>
+        <v>0.3039499819278717</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.01727030239999294</v>
+        <v>0.4159094989299774</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.003198799444362521</v>
+        <v>0.1401475369930267</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.01402466651052237</v>
+        <v>0.07935599982738495</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.003632037900388241</v>
+        <v>0.08680334687232971</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.03202337026596069</v>
+        <v>0.4101364612579346</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.006340515799820423</v>
+        <v>0.04013556614518166</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.04165037348866463</v>
+        <v>0.508473813533783</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.07853895425796509</v>
+        <v>0.3700691759586334</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.008348770439624786</v>
+        <v>0.7291043400764465</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.01268526539206505</v>
+        <v>0.7180308699607849</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.02452272735536098</v>
+        <v>0.06573512405157089</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.001037287525832653</v>
+        <v>0.08663393557071686</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.01251252740621567</v>
+        <v>0.00667689461261034</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.02186241559684277</v>
+        <v>0.1288582980632782</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.008176793344318867</v>
+        <v>0.1521118879318237</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.01363214105367661</v>
+        <v>0.2742851972579956</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.005268712993711233</v>
+        <v>0.02417942881584167</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.001482115127146244</v>
+        <v>0.4867962002754211</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.07514131814241409</v>
+        <v>0.4398671984672546</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.03655543178319931</v>
+        <v>0.05656523257493973</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.0737152174115181</v>
+        <v>0.4809225499629974</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.01062228251248598</v>
+        <v>0.4336986243724823</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.002015868201851845</v>
+        <v>0.1552585512399673</v>
       </c>
     </row>
     <row r="3">
@@ -2137,1709 +2137,6830 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.311824232339859</v>
+        <v>0.01453255582600832</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06529183685779572</v>
+        <v>0.001682458445429802</v>
       </c>
       <c r="C4" t="n">
-        <v>0.327763557434082</v>
+        <v>0.003079592017456889</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08535347878932953</v>
+        <v>0.002693227725103498</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1472960412502289</v>
+        <v>0.009341050870716572</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1487185657024384</v>
+        <v>0.01024501584470272</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2288483083248138</v>
+        <v>0.003889308776706457</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08512403815984726</v>
+        <v>0.008811124600470066</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02842977270483971</v>
+        <v>0.004054398275911808</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1332777142524719</v>
+        <v>0.01658325828611851</v>
       </c>
       <c r="K4" t="n">
-        <v>0.196737676858902</v>
+        <v>0.008117890916764736</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2291845232248306</v>
+        <v>0.00300682638771832</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03392749279737473</v>
+        <v>0.007477270904928446</v>
       </c>
       <c r="N4" t="n">
-        <v>0.269484281539917</v>
+        <v>0.002556064864620566</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2635709643363953</v>
+        <v>0.009754768572747707</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1195966526865959</v>
+        <v>0.01100799348205328</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08081704378128052</v>
+        <v>0.006642608903348446</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03604341298341751</v>
+        <v>7.02831894159317e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05451307073235512</v>
+        <v>0.001559537020511925</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0590132363140583</v>
+        <v>0.0009537399164400995</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1673479974269867</v>
+        <v>0.002575511578470469</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1112671196460724</v>
+        <v>0.0008230172097682953</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02894737757742405</v>
+        <v>0.002576880855485797</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1444024443626404</v>
+        <v>0.0006045205518603325</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09584659337997437</v>
+        <v>0.002392921131104231</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1892405599355698</v>
+        <v>0.001826011459343135</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03125878423452377</v>
+        <v>0.001490353955887258</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.09251925349235535</v>
+        <v>0.004133371170610189</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1051106005907059</v>
+        <v>0.003012060886248946</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.03238937631249428</v>
+        <v>0.0002942633000202477</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.08809136599302292</v>
+        <v>0.005613239016383886</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0942707285284996</v>
+        <v>0.004373569972813129</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.07459716498851776</v>
+        <v>0.002116193063557148</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.04157250747084618</v>
+        <v>0.001174642704427242</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.1357477754354477</v>
+        <v>0.005135811865329742</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.02717815712094307</v>
+        <v>0.0006331364857032895</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.1027263477444649</v>
+        <v>0.0007509423885494471</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0193202942609787</v>
+        <v>0.002367308828979731</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.02698555961251259</v>
+        <v>0.0004142631078138947</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.009083673357963562</v>
+        <v>0.001021970994770527</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.2050426006317139</v>
+        <v>0.002247171243652701</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.02829062566161156</v>
+        <v>0.0012588647659868</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.02283478155732155</v>
+        <v>0.001720739644952118</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.03277003392577171</v>
+        <v>0.001086257863789797</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.01518157403916121</v>
+        <v>0.0009007799671962857</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.1187636181712151</v>
+        <v>0.01514933258295059</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1722923517227173</v>
+        <v>0.005387314595282078</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.3144979476928711</v>
+        <v>0.005146931856870651</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.03158725425601006</v>
+        <v>0.005772512406110764</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.2322647720575333</v>
+        <v>0.004802392330020666</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.2156004011631012</v>
+        <v>0.002070801798254251</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1206143349409103</v>
+        <v>0.002498484682291746</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.150520533323288</v>
+        <v>0.00673907995223999</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.1507184356451035</v>
+        <v>0.0005894505884498358</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.2021131068468094</v>
+        <v>0.003230052534490824</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02585725486278534</v>
+        <v>0.002058519050478935</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.02200246602296829</v>
+        <v>0.0004362259642221034</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0407833643257618</v>
+        <v>0.005020014941692352</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.04050222784280777</v>
+        <v>0.008215956389904022</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.2888465225696564</v>
+        <v>0.00475076399743557</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.1117720603942871</v>
+        <v>0.002293357392773032</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.1205533370375633</v>
+        <v>2.996134571731091e-05</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.2024897336959839</v>
+        <v>0.001758539583534002</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.02414325252175331</v>
+        <v>0.003313433844596148</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.2398727536201477</v>
+        <v>0.002597978804260492</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.2695529758930206</v>
+        <v>0.0001206865272251889</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.1499715745449066</v>
+        <v>0.00555367860943079</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1713221520185471</v>
+        <v>0.005160414148122072</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.1270493865013123</v>
+        <v>0.003012967761605978</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.03761940822005272</v>
+        <v>0.001307471771724522</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.08615969121456146</v>
+        <v>0.005108220968395472</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.05265884473919868</v>
+        <v>0.002139756921678782</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.1195103004574776</v>
+        <v>0.004581538494676352</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1158753111958504</v>
+        <v>0.001563483383506536</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.09745366871356964</v>
+        <v>0.005068334750831127</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.04206123948097229</v>
+        <v>0.0004831492842640728</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.09805533289909363</v>
+        <v>0.001902979332953691</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.123550146818161</v>
+        <v>0.001340748160146177</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.08235225081443787</v>
+        <v>0.001718373969197273</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.126410573720932</v>
+        <v>0.002161514945328236</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.09442362934350967</v>
+        <v>0.004200224298983812</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.06236846745014191</v>
+        <v>0.0034899334423244</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.1669858247041702</v>
+        <v>0.002917393809184432</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.05593182519078255</v>
+        <v>0.0009179964545182884</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.08642676472663879</v>
+        <v>0.00232671108096838</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.01953584142029285</v>
+        <v>0.0004529164871200919</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.04191729426383972</v>
+        <v>0.002053760457783937</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.02448697946965694</v>
+        <v>0.002831176854670048</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.09231822937726974</v>
+        <v>0.0005282873753458261</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0003191647119820118</v>
+        <v>0.001067714300006628</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.111450307071209</v>
+        <v>0.000302391592413187</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.02581241726875305</v>
+        <v>0.005866739898920059</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0802474319934845</v>
+        <v>0.001215356402099133</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.06999782472848892</v>
+        <v>0.006852784194052219</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.3913150429725647</v>
+        <v>0.003337008878588676</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.1350214779376984</v>
+        <v>0.004886583425104618</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0408003181219101</v>
+        <v>0.01199144031852484</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.1080616116523743</v>
+        <v>0.009150715544819832</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.03938253223896027</v>
+        <v>0.004166000988334417</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.03942392393946648</v>
+        <v>0.003391649574041367</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.16606305539608</v>
+        <v>0.003491268493235111</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.04322516173124313</v>
+        <v>0.0001154687270172872</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.06502916663885117</v>
+        <v>0.00197283667512238</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.04046766087412834</v>
+        <v>0.00159526348579675</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.004420134704560041</v>
+        <v>0.001619192771613598</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.01797285303473473</v>
+        <v>0.002212019637227058</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.09915787726640701</v>
+        <v>1.250958302989602e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.01805193722248077</v>
+        <v>0.0004776381538249552</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.09297539293766022</v>
+        <v>0.004493233282119036</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.04545147344470024</v>
+        <v>0.00706777349114418</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.1194314360618591</v>
+        <v>0.002287284238263965</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.5239636898040771</v>
+        <v>0.0004297769046388566</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1154178380966187</v>
+        <v>0.004935709293931723</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.101477637887001</v>
+        <v>0.004333911929279566</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.1357403695583344</v>
+        <v>0.0005353440064936876</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.103739470243454</v>
+        <v>4.918163176625967e-05</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.06376137584447861</v>
+        <v>0.006000972352921963</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.05511845275759697</v>
+        <v>0.003778459271416068</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.05843885615468025</v>
+        <v>0.00243935757316649</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.03182718902826309</v>
+        <v>0.00100153882522136</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.1377776712179184</v>
+        <v>0.001363704912364483</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.06736652553081512</v>
+        <v>0.001794314477592707</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0443422794342041</v>
+        <v>0.002076582051813602</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.006092104129493237</v>
+        <v>0.002380703343078494</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.1783376485109329</v>
+        <v>0.001161827705800533</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.02863056212663651</v>
+        <v>0.000526965653989464</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.08683552592992783</v>
+        <v>0.0003412014339119196</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.2075758427381516</v>
+        <v>0.0006111030234023929</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.04303770139813423</v>
+        <v>0.001448343158699572</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.01481486670672894</v>
+        <v>0.003039158415049314</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.06175066903233528</v>
+        <v>0.001117011648602784</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.02681896463036537</v>
+        <v>0.004072513431310654</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.00360465981066227</v>
+        <v>0.00196343008428812</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.1002159342169762</v>
+        <v>0.0007173818303272128</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.01391526311635971</v>
+        <v>0.00120404246263206</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.02314982935786247</v>
+        <v>0.001208791276440024</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.1749449670314789</v>
+        <v>0.001585269812494516</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.04768680036067963</v>
+        <v>0.0002734584559220821</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.1173054277896881</v>
+        <v>0.006053930148482323</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.01017017103731632</v>
+        <v>0.001358671113848686</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.1324568241834641</v>
+        <v>0.002150411019101739</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.002220273017883301</v>
+        <v>0.00481474120169878</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.04199076071381569</v>
+        <v>0.002375073963776231</v>
       </c>
       <c r="EN4" t="n">
-        <v>4.629697650671005e-05</v>
+        <v>0.0002424350241199136</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.03486083820462227</v>
+        <v>0.003042127937078476</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.09424134343862534</v>
+        <v>0.005196819547563791</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.02880853042006493</v>
+        <v>0.001889083650894463</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.08416153490543365</v>
+        <v>0.00591687485575676</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.07614383101463318</v>
+        <v>0.003517934819683433</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.01799257472157478</v>
+        <v>0.004441069904714823</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.02682022750377655</v>
+        <v>0.001768818590790033</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.07647876441478729</v>
+        <v>0.001254694070667028</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0382193997502327</v>
+        <v>0.002954513300210238</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.05528993159532547</v>
+        <v>0.003357559675350785</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.1200087144970894</v>
+        <v>0.003795152762904763</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.04551561549305916</v>
+        <v>0.0003076172433793545</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.06544622778892517</v>
+        <v>0.0003264774277340621</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.04322616755962372</v>
+        <v>0.0002176724374294281</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0466102659702301</v>
+        <v>0.002343400148674846</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.06339909881353378</v>
+        <v>0.003657623659819365</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.1468247473239899</v>
+        <v>0.001494975411333144</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.00354383559897542</v>
+        <v>0.002110082888975739</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.1276356875896454</v>
+        <v>0.008975383825600147</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.1374664753675461</v>
+        <v>7.117260247468948e-05</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.08233156055212021</v>
+        <v>0.002673585899174213</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.03146621957421303</v>
+        <v>0.004375977907329798</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.1167172268033028</v>
+        <v>0.0001990285236388445</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.02857674285769463</v>
+        <v>0.0002556664985604584</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0632263571023941</v>
+        <v>0.002528883051127195</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.08906824886798859</v>
+        <v>0.0009323614649474621</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.04576673358678818</v>
+        <v>0.001013446599245071</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0846002995967865</v>
+        <v>0.006159662269055843</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.1155950278043747</v>
+        <v>0.01978649012744427</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.1107779517769814</v>
+        <v>0.004869163502007723</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.05965980142354965</v>
+        <v>0.007421179674565792</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.1670784801244736</v>
+        <v>0.01227135490626097</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.2620780169963837</v>
+        <v>0.001252081943675876</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.02264805510640144</v>
+        <v>0.0007968965219333768</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0002737417817115784</v>
+        <v>0.008867145515978336</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.03603598475456238</v>
+        <v>0.003398791188374162</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.002344923093914986</v>
+        <v>0.004053906537592411</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.2016126066446304</v>
+        <v>0.005152462515980005</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.08471300452947617</v>
+        <v>0.003234849311411381</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.09833893924951553</v>
+        <v>0.006338496692478657</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.1445963233709335</v>
+        <v>0.005794497672468424</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.1799743175506592</v>
+        <v>0.004065956454724073</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.09219358861446381</v>
+        <v>0.006024197209626436</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.1244314312934875</v>
+        <v>0.00215639011003077</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0185022596269846</v>
+        <v>0.001182963838800788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.57856527241529e-06</v>
+        <v>0.02023673243820667</v>
       </c>
       <c r="B5" t="n">
-        <v>2.149303782061907e-06</v>
+        <v>0.6481934785842896</v>
       </c>
       <c r="C5" t="n">
-        <v>1.767442654454499e-06</v>
+        <v>0.01320288330316544</v>
       </c>
       <c r="D5" t="n">
-        <v>9.354284884466324e-07</v>
+        <v>0.8994227647781372</v>
       </c>
       <c r="E5" t="n">
-        <v>1.334815692644042e-06</v>
+        <v>0.2059255689382553</v>
       </c>
       <c r="F5" t="n">
-        <v>8.448230346402852e-07</v>
+        <v>0.1110686212778091</v>
       </c>
       <c r="G5" t="n">
-        <v>2.178760269089253e-06</v>
+        <v>0.2989845871925354</v>
       </c>
       <c r="H5" t="n">
-        <v>1.639028937461262e-06</v>
+        <v>0.3567063510417938</v>
       </c>
       <c r="I5" t="n">
-        <v>1.941082018674933e-06</v>
+        <v>0.02902115136384964</v>
       </c>
       <c r="J5" t="n">
-        <v>3.045782705157762e-06</v>
+        <v>0.0253214742988348</v>
       </c>
       <c r="K5" t="n">
-        <v>1.538728611194529e-06</v>
+        <v>0.5230001211166382</v>
       </c>
       <c r="L5" t="n">
-        <v>5.542239591704856e-07</v>
+        <v>0.01092724502086639</v>
       </c>
       <c r="M5" t="n">
-        <v>1.453211666557763e-07</v>
+        <v>1.17673659324646</v>
       </c>
       <c r="N5" t="n">
-        <v>1.680016566751874e-06</v>
+        <v>0.2413681447505951</v>
       </c>
       <c r="O5" t="n">
-        <v>1.064287175722711e-06</v>
+        <v>0.02845699712634087</v>
       </c>
       <c r="P5" t="n">
-        <v>2.648464715093723e-06</v>
+        <v>0.4231668710708618</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.293633204113576e-06</v>
+        <v>0.09727395325899124</v>
       </c>
       <c r="R5" t="n">
-        <v>2.551921625126852e-06</v>
+        <v>0.06234132125973701</v>
       </c>
       <c r="S5" t="n">
-        <v>6.121467777120415e-08</v>
+        <v>0.02492744103074074</v>
       </c>
       <c r="T5" t="n">
-        <v>6.651865191997786e-07</v>
+        <v>0.04538672789931297</v>
       </c>
       <c r="U5" t="n">
-        <v>1.069942527465173e-06</v>
+        <v>0.07288624346256256</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27917155623436e-06</v>
+        <v>0.05442168563604355</v>
       </c>
       <c r="W5" t="n">
-        <v>8.981052133094636e-07</v>
+        <v>0.03083853423595428</v>
       </c>
       <c r="X5" t="n">
-        <v>2.139924220045941e-07</v>
+        <v>0.09969238191843033</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.423363174690166e-08</v>
+        <v>0.003568887710571289</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.892895108492667e-07</v>
+        <v>0.1373437792062759</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.543094847686007e-07</v>
+        <v>0.05623511970043182</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.140188482575468e-07</v>
+        <v>0.02039914019405842</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.544796305097407e-06</v>
+        <v>0.1171552687883377</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.546122115949402e-07</v>
+        <v>0.05139156430959702</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.000715087684512e-06</v>
+        <v>0.03162862733006477</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.251053163286997e-06</v>
+        <v>0.09254105389118195</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.81617758446373e-07</v>
+        <v>0.05864777788519859</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.54112842160248e-07</v>
+        <v>0.08625601232051849</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.111652068175317e-06</v>
+        <v>0.06813287734985352</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5.349910381369227e-08</v>
+        <v>0.1316798031330109</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.696845567446871e-07</v>
+        <v>0.05753997340798378</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.170208119878225e-07</v>
+        <v>0.2703295350074768</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.054209602420087e-07</v>
+        <v>0.06452856957912445</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.468862137699034e-06</v>
+        <v>0.1659402847290039</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.726526299236866e-07</v>
+        <v>0.2221914678812027</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.881198500086612e-06</v>
+        <v>0.1470618844032288</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.519219322039135e-07</v>
+        <v>0.09176439046859741</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.830355113786936e-08</v>
+        <v>0.1496590226888657</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.309086314904562e-07</v>
+        <v>0.03852730244398117</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.678776584412844e-08</v>
+        <v>0.01530777662992477</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.477709585946286e-06</v>
+        <v>0.3705784380435944</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.153632294721319e-06</v>
+        <v>0.002122070640325546</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.836867108475417e-06</v>
+        <v>0.4201596975326538</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.341756488836836e-06</v>
+        <v>0.3501604199409485</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.429087660653749e-06</v>
+        <v>0.02172248996794224</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.16668593364011e-06</v>
+        <v>0.05142170935869217</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.415509470665711e-06</v>
+        <v>0.05964957922697067</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.708968170532899e-06</v>
+        <v>0.1666590124368668</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.525483412478934e-06</v>
+        <v>0.03467351198196411</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.842682761183823e-06</v>
+        <v>0.02152582257986069</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.243063986246852e-07</v>
+        <v>0.05896627157926559</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.798950617943774e-07</v>
+        <v>0.1135379076004028</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.998403260789928e-06</v>
+        <v>0.02937203273177147</v>
       </c>
       <c r="BH5" t="n">
-        <v>1.075567865882476e-06</v>
+        <v>0.1230272576212883</v>
       </c>
       <c r="BI5" t="n">
-        <v>8.816906529318658e-07</v>
+        <v>0.03622464090585709</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.321652462138445e-06</v>
+        <v>0.04673116654157639</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.31437637568888e-07</v>
+        <v>0.2145457714796066</v>
       </c>
       <c r="BL5" t="n">
-        <v>6.408168928828673e-07</v>
+        <v>0.0449361577630043</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.478981403124635e-06</v>
+        <v>0.02767449617385864</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.129071961258887e-06</v>
+        <v>0.04937450587749481</v>
       </c>
       <c r="BO5" t="n">
-        <v>2.827538310157252e-07</v>
+        <v>0.05509737133979797</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.68340795628319e-06</v>
+        <v>0.01740013062953949</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.762551371750305e-07</v>
+        <v>0.08168822526931763</v>
       </c>
       <c r="BR5" t="n">
-        <v>1.585668769621407e-07</v>
+        <v>0.06071700528264046</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.520226171844115e-07</v>
+        <v>0.05482490360736847</v>
       </c>
       <c r="BT5" t="n">
-        <v>2.795055934257107e-06</v>
+        <v>0.07394839823246002</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.803727738864836e-07</v>
+        <v>0.01569041982293129</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.531498908974754e-07</v>
+        <v>0.3178397715091705</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.323285090393256e-07</v>
+        <v>0.01977994292974472</v>
       </c>
       <c r="BX5" t="n">
-        <v>2.555074161136872e-06</v>
+        <v>0.3289646506309509</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.384330739208963e-06</v>
+        <v>0.07272143661975861</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.49235631852207e-07</v>
+        <v>0.07382642477750778</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.61197611609532e-07</v>
+        <v>0.07766787707805634</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.725735273794271e-06</v>
+        <v>0.07323093712329865</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.557279626420495e-08</v>
+        <v>0.02690920606255531</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.778121021648985e-07</v>
+        <v>0.005550525616854429</v>
       </c>
       <c r="CE5" t="n">
-        <v>3.41864023312155e-07</v>
+        <v>0.2242494225502014</v>
       </c>
       <c r="CF5" t="n">
-        <v>5.760279009336955e-07</v>
+        <v>0.0006415192037820816</v>
       </c>
       <c r="CG5" t="n">
-        <v>1.121427999350999e-06</v>
+        <v>0.3046126365661621</v>
       </c>
       <c r="CH5" t="n">
-        <v>2.229367765949064e-07</v>
+        <v>0.002278398955240846</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.04413493318134e-06</v>
+        <v>0.00968517828732729</v>
       </c>
       <c r="CJ5" t="n">
-        <v>4.091409664397361e-07</v>
+        <v>0.01459795981645584</v>
       </c>
       <c r="CK5" t="n">
-        <v>2.852428053756739e-07</v>
+        <v>0.1000641137361526</v>
       </c>
       <c r="CL5" t="n">
-        <v>8.42631720843201e-07</v>
+        <v>0.0355522558093071</v>
       </c>
       <c r="CM5" t="n">
-        <v>5.413827466327348e-07</v>
+        <v>0.01915620639920235</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.471560492267599e-06</v>
+        <v>0.3541736900806427</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.816307985791354e-06</v>
+        <v>0.09375517070293427</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.937525212269975e-06</v>
+        <v>0.4492779970169067</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.416921461190213e-06</v>
+        <v>0.01893465593457222</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.991092631214997e-06</v>
+        <v>0.05553180351853371</v>
       </c>
       <c r="CS5" t="n">
-        <v>4.00616841034207e-07</v>
+        <v>0.06709659844636917</v>
       </c>
       <c r="CT5" t="n">
-        <v>1.547106990074099e-06</v>
+        <v>0.009839995764195919</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.357329210804892e-06</v>
+        <v>0.004858114756643772</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.67038956280885e-07</v>
+        <v>0.0009418139234185219</v>
       </c>
       <c r="CW5" t="n">
-        <v>4.999669158678444e-07</v>
+        <v>0.2221534997224808</v>
       </c>
       <c r="CX5" t="n">
-        <v>7.375159611910931e-07</v>
+        <v>0.01455454435199499</v>
       </c>
       <c r="CY5" t="n">
-        <v>9.787822818907443e-07</v>
+        <v>0.3195206224918365</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.492032275507427e-08</v>
+        <v>0.02492586150765419</v>
       </c>
       <c r="DA5" t="n">
-        <v>3.330566187287332e-07</v>
+        <v>0.003158189821988344</v>
       </c>
       <c r="DB5" t="n">
-        <v>4.774356057168916e-07</v>
+        <v>0.03981293737888336</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.596601748588e-07</v>
+        <v>0.1119745448231697</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.00588363238785e-06</v>
+        <v>0.0230732262134552</v>
       </c>
       <c r="DE5" t="n">
-        <v>3.978871347953827e-07</v>
+        <v>0.04723792150616646</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.230743575637462e-06</v>
+        <v>0.1699821054935455</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.837180540562258e-07</v>
+        <v>0.07963870465755463</v>
       </c>
       <c r="DH5" t="n">
-        <v>9.671352927398402e-07</v>
+        <v>0.2736482620239258</v>
       </c>
       <c r="DI5" t="n">
-        <v>6.95668495609425e-06</v>
+        <v>0.05206210911273956</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4.325489953771466e-06</v>
+        <v>0.1142155528068542</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.444981080567231e-06</v>
+        <v>0.0002225190401077271</v>
       </c>
       <c r="DL5" t="n">
-        <v>7.636576242475712e-07</v>
+        <v>0.3631475567817688</v>
       </c>
       <c r="DM5" t="n">
-        <v>2.129423592123203e-06</v>
+        <v>0.1093125343322754</v>
       </c>
       <c r="DN5" t="n">
-        <v>5.060628041064774e-07</v>
+        <v>0.01992343738675117</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.599980123501155e-06</v>
+        <v>0.1085605174303055</v>
       </c>
       <c r="DP5" t="n">
-        <v>4.634534320757666e-07</v>
+        <v>0.009168314747512341</v>
       </c>
       <c r="DQ5" t="n">
-        <v>1.044339683176077e-06</v>
+        <v>0.1490852236747742</v>
       </c>
       <c r="DR5" t="n">
-        <v>3.624951204983518e-06</v>
+        <v>0.05743261426687241</v>
       </c>
       <c r="DS5" t="n">
-        <v>5.986837550153723e-07</v>
+        <v>0.01054277829825878</v>
       </c>
       <c r="DT5" t="n">
-        <v>4.915170848107664e-08</v>
+        <v>0.09955564141273499</v>
       </c>
       <c r="DU5" t="n">
-        <v>1.927922710365237e-07</v>
+        <v>0.08721141517162323</v>
       </c>
       <c r="DV5" t="n">
-        <v>7.468709668501106e-07</v>
+        <v>0.3644851446151733</v>
       </c>
       <c r="DW5" t="n">
-        <v>1.587299038874335e-07</v>
+        <v>0.04354709014296532</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.140604808824719e-06</v>
+        <v>0.0765516608953476</v>
       </c>
       <c r="DY5" t="n">
-        <v>2.99624758781647e-07</v>
+        <v>0.1578516662120819</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.310675987857394e-07</v>
+        <v>0.1886080205440521</v>
       </c>
       <c r="EA5" t="n">
-        <v>4.039710006509267e-07</v>
+        <v>0.09703319519758224</v>
       </c>
       <c r="EB5" t="n">
-        <v>4.813738314624061e-07</v>
+        <v>0.1483331173658371</v>
       </c>
       <c r="EC5" t="n">
-        <v>5.904730642214417e-07</v>
+        <v>0.04056276381015778</v>
       </c>
       <c r="ED5" t="n">
-        <v>4.299418776554376e-07</v>
+        <v>0.3921052515506744</v>
       </c>
       <c r="EE5" t="n">
-        <v>1.05395236005279e-06</v>
+        <v>0.2236340939998627</v>
       </c>
       <c r="EF5" t="n">
-        <v>9.936286460288102e-07</v>
+        <v>0.1536319106817245</v>
       </c>
       <c r="EG5" t="n">
-        <v>4.063537915044435e-07</v>
+        <v>0.1931786984205246</v>
       </c>
       <c r="EH5" t="n">
-        <v>1.307440470554866e-06</v>
+        <v>0.1164581328630447</v>
       </c>
       <c r="EI5" t="n">
-        <v>1.105223418562673e-06</v>
+        <v>0.2215596288442612</v>
       </c>
       <c r="EJ5" t="n">
-        <v>9.851479632061455e-09</v>
+        <v>0.07942252606153488</v>
       </c>
       <c r="EK5" t="n">
-        <v>2.743139049243837e-10</v>
+        <v>0.02450019493699074</v>
       </c>
       <c r="EL5" t="n">
-        <v>3.668632757580781e-07</v>
+        <v>0.01364757493138313</v>
       </c>
       <c r="EM5" t="n">
-        <v>9.733378192322562e-07</v>
+        <v>0.09169707447290421</v>
       </c>
       <c r="EN5" t="n">
-        <v>1.377648231937201e-06</v>
+        <v>0.02504361420869827</v>
       </c>
       <c r="EO5" t="n">
-        <v>5.050958407082362e-07</v>
+        <v>0.05651960149407387</v>
       </c>
       <c r="EP5" t="n">
-        <v>7.453955959135783e-07</v>
+        <v>0.2152489721775055</v>
       </c>
       <c r="EQ5" t="n">
-        <v>1.079887624655385e-06</v>
+        <v>0.1275100857019424</v>
       </c>
       <c r="ER5" t="n">
-        <v>3.357619789312594e-06</v>
+        <v>0.2200030237436295</v>
       </c>
       <c r="ES5" t="n">
-        <v>2.074914846161846e-06</v>
+        <v>0.1296665668487549</v>
       </c>
       <c r="ET5" t="n">
-        <v>7.815463618499052e-07</v>
+        <v>0.1075530052185059</v>
       </c>
       <c r="EU5" t="n">
-        <v>5.35385993316595e-08</v>
+        <v>0.1057583689689636</v>
       </c>
       <c r="EV5" t="n">
-        <v>6.553768798767123e-07</v>
+        <v>0.1229333430528641</v>
       </c>
       <c r="EW5" t="n">
-        <v>9.87269800134527e-07</v>
+        <v>0.1033045276999474</v>
       </c>
       <c r="EX5" t="n">
-        <v>4.853434347751318e-07</v>
+        <v>0.004514322616159916</v>
       </c>
       <c r="EY5" t="n">
-        <v>1.043534467726204e-07</v>
+        <v>0.2683584690093994</v>
       </c>
       <c r="EZ5" t="n">
-        <v>6.910022989359277e-07</v>
+        <v>0.01463185623288155</v>
       </c>
       <c r="FA5" t="n">
-        <v>8.850215067468525e-07</v>
+        <v>0.3525768518447876</v>
       </c>
       <c r="FB5" t="n">
-        <v>4.082396003468602e-07</v>
+        <v>0.01169990934431553</v>
       </c>
       <c r="FC5" t="n">
-        <v>4.482638473746192e-07</v>
+        <v>0.002113561611622572</v>
       </c>
       <c r="FD5" t="n">
-        <v>4.492664515964861e-07</v>
+        <v>0.02468804083764553</v>
       </c>
       <c r="FE5" t="n">
-        <v>4.330840397415159e-07</v>
+        <v>0.152602806687355</v>
       </c>
       <c r="FF5" t="n">
-        <v>6.834757755314058e-07</v>
+        <v>0.02733767777681351</v>
       </c>
       <c r="FG5" t="n">
-        <v>8.973528053957125e-08</v>
+        <v>0.008787993341684341</v>
       </c>
       <c r="FH5" t="n">
-        <v>6.681461854896042e-07</v>
+        <v>0.08145231008529663</v>
       </c>
       <c r="FI5" t="n">
-        <v>6.642478922458395e-08</v>
+        <v>0.08225828409194946</v>
       </c>
       <c r="FJ5" t="n">
-        <v>5.739617563449428e-07</v>
+        <v>0.1125040426850319</v>
       </c>
       <c r="FK5" t="n">
-        <v>7.163984605540463e-07</v>
+        <v>0.01207929011434317</v>
       </c>
       <c r="FL5" t="n">
-        <v>9.299025123254978e-07</v>
+        <v>0.06634631007909775</v>
       </c>
       <c r="FM5" t="n">
-        <v>9.023551683640108e-07</v>
+        <v>0.05514546483755112</v>
       </c>
       <c r="FN5" t="n">
-        <v>6.498638072116592e-08</v>
+        <v>0.05953929573297501</v>
       </c>
       <c r="FO5" t="n">
-        <v>2.963138001632615e-07</v>
+        <v>0.2070311158895493</v>
       </c>
       <c r="FP5" t="n">
-        <v>3.673982007512677e-07</v>
+        <v>0.09883805364370346</v>
       </c>
       <c r="FQ5" t="n">
-        <v>1.074165425052342e-06</v>
+        <v>0.4118665456771851</v>
       </c>
       <c r="FR5" t="n">
-        <v>2.231166490673786e-06</v>
+        <v>0.1575949788093567</v>
       </c>
       <c r="FS5" t="n">
-        <v>1.630164547350432e-06</v>
+        <v>0.2777711749076843</v>
       </c>
       <c r="FT5" t="n">
-        <v>5.057525868323864e-06</v>
+        <v>0.01292357221245766</v>
       </c>
       <c r="FU5" t="n">
-        <v>1.219664000018383e-06</v>
+        <v>0.0537102073431015</v>
       </c>
       <c r="FV5" t="n">
-        <v>1.759267888701288e-06</v>
+        <v>0.1095956861972809</v>
       </c>
       <c r="FW5" t="n">
-        <v>1.425757773176883e-06</v>
+        <v>0.04240549728274345</v>
       </c>
       <c r="FX5" t="n">
-        <v>2.03647618945979e-06</v>
+        <v>0.2692059576511383</v>
       </c>
       <c r="FY5" t="n">
-        <v>7.708889597779489e-07</v>
+        <v>0.08582738041877747</v>
       </c>
       <c r="FZ5" t="n">
-        <v>3.113981961178069e-07</v>
+        <v>0.1280089914798737</v>
       </c>
       <c r="GA5" t="n">
-        <v>1.605703801033087e-06</v>
+        <v>0.01190124452114105</v>
       </c>
       <c r="GB5" t="n">
-        <v>2.50244033850322e-06</v>
+        <v>0.2310968041419983</v>
       </c>
       <c r="GC5" t="n">
-        <v>4.686942247644765e-06</v>
+        <v>0.2810845077037811</v>
       </c>
       <c r="GD5" t="n">
-        <v>2.881626869566389e-06</v>
+        <v>0.04064386337995529</v>
       </c>
       <c r="GE5" t="n">
-        <v>8.927767680688703e-07</v>
+        <v>0.1861837357282639</v>
       </c>
       <c r="GF5" t="n">
-        <v>2.509622618163121e-06</v>
+        <v>0.198974534869194</v>
       </c>
       <c r="GG5" t="n">
-        <v>5.382323138292122e-07</v>
+        <v>0.03949452936649323</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>0.005541519727557898</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.01212153490632772</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>9.42242331802845e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.001074146828614175</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.000998608535155654</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.0125114107504487</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.004949102178215981</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.003544909646734595</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.003726791590452194</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.00579496705904603</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.01549949217587709</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.001470794319175184</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.00172463629860431</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.002771284431219101</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.0116808544844389</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.003097512992098927</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.000358526362106204</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.007490591611713171</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.0002055058284895495</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.000496341148391366</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.0031058294698596</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.002602723892778158</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.001853504334576428</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.001620318042114377</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.0006157407769933343</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>0.003647407051175833</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>0.001288270344957709</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>4.415749572217464e-06</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>0.002287672134116292</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>0.001511830952949822</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>0.00191649526823312</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.005268419627100229</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>0.00135874142870307</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>0.0006202078075148165</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>0.00572775537148118</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>5.150540528120473e-05</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>0.001320047187618911</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>0.001939720124937594</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>0.002514964900910854</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>0.002716877264901996</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>0.0009146498050540686</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>0.001013352652080357</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>0.001655127853155136</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>0.004366039764136076</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>0.002026484813541174</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>0.00437827967107296</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>0.01151340268552303</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.002329354174435139</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.0005146545590832829</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>0.002827460411936045</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>0.006857930216938257</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>0.0001005622907541692</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>0.001530854729935527</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>0.001871410408057272</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>0.0007323101162910461</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>0.002038049511611462</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>0.001148068578913808</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>0.0001288745552301407</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>0.001259372103959322</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>0.003694261191412807</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>0.001957110362127423</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>0.001884822733700275</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>0.002718772040680051</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>0.0002163772587664425</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>0.002835772465914488</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>0.0003476396959740669</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>3.566441591829062e-06</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>0.003201497253030539</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>0.001523768180049956</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>0.004979676101356745</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>0.0002220487804152071</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>0.003087207674980164</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>0.001617783214896917</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>0.006996182724833488</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>0.001654247753322124</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>0.004154578782618046</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>0.000336882658302784</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>0.003868924453854561</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>0.0009626371902413666</v>
       </c>
       <c r="CB6" t="n">
-        <v>0</v>
+        <v>0.0005866822903044522</v>
       </c>
       <c r="CC6" t="n">
-        <v>0</v>
+        <v>0.001474088057875633</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>0.002316949423402548</v>
       </c>
       <c r="CE6" t="n">
-        <v>0</v>
+        <v>0.003608991159126163</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>0.0007904103258624673</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>0.0006446114857681096</v>
       </c>
       <c r="CH6" t="n">
-        <v>0</v>
+        <v>0.001287686754949391</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>0.003134163562208414</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>0.002136217197403312</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>0.0008518768008798361</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>0.0006971710245124996</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>0.00102883973158896</v>
       </c>
       <c r="CN6" t="n">
-        <v>0</v>
+        <v>0.006501671392470598</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>0.002191236242651939</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>0.002212206600233912</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0</v>
+        <v>0.00250444863922894</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>0.001309479819610715</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>0.001025358564220369</v>
       </c>
       <c r="CT6" t="n">
-        <v>0</v>
+        <v>0.001438260427676141</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>5.341814176063053e-05</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>0.001689756638370454</v>
       </c>
       <c r="CW6" t="n">
-        <v>0</v>
+        <v>0.00327399093657732</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>0.0006172466091811657</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>0.0003244997351430357</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0</v>
+        <v>0.001045920187607408</v>
       </c>
       <c r="DA6" t="n">
-        <v>0</v>
+        <v>0.003068331861868501</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>0.00103820557706058</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>0.001298484043218195</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>0.0008048961171880364</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>0.000748867925722152</v>
       </c>
       <c r="DF6" t="n">
-        <v>0</v>
+        <v>0.004148566164076328</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>0.002448613755404949</v>
       </c>
       <c r="DH6" t="n">
-        <v>0</v>
+        <v>0.0004740504082292318</v>
       </c>
       <c r="DI6" t="n">
-        <v>0</v>
+        <v>0.005325795151293278</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>0.004762591328471899</v>
       </c>
       <c r="DK6" t="n">
-        <v>0</v>
+        <v>0.0002675624564290047</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>0.00292768981307745</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>0.00107341876719147</v>
       </c>
       <c r="DN6" t="n">
-        <v>0</v>
+        <v>0.001205954002216458</v>
       </c>
       <c r="DO6" t="n">
-        <v>0</v>
+        <v>0.002090620808303356</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>0.001427307375706732</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0</v>
+        <v>0.002727814018726349</v>
       </c>
       <c r="DR6" t="n">
-        <v>0</v>
+        <v>0.001369392033666372</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>0.0037604128010571</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>0.0009741794201545417</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>0.004336004145443439</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>0.001307065482251346</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>0.001810018671676517</v>
       </c>
       <c r="DX6" t="n">
-        <v>0</v>
+        <v>0.0005796455079689622</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>0.0006270271260291338</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>0.001588950864970684</v>
       </c>
       <c r="EA6" t="n">
-        <v>0</v>
+        <v>0.001791933202184737</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>0.003414787352085114</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>0.000201499555259943</v>
       </c>
       <c r="ED6" t="n">
-        <v>0</v>
+        <v>0.002792072016745806</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>0.004162188619375229</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>0.002256067236885428</v>
       </c>
       <c r="EG6" t="n">
-        <v>0</v>
+        <v>6.122294871602207e-05</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>0.002322384621948004</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>6.128317909315228e-05</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0</v>
+        <v>0.00226557394489646</v>
       </c>
       <c r="EK6" t="n">
-        <v>0</v>
+        <v>0.001601050607860088</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>0.001488892827183008</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>0.0001334243570454419</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>0.0002068812900688499</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>0.002042077947407961</v>
       </c>
       <c r="EP6" t="n">
-        <v>0</v>
+        <v>0.001158973202109337</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>1.886123209260404e-05</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>0.001687871641479433</v>
       </c>
       <c r="ES6" t="n">
-        <v>0</v>
+        <v>0.00337756727822125</v>
       </c>
       <c r="ET6" t="n">
-        <v>0</v>
+        <v>0.003721390850841999</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>0.0007516822079196572</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>4.911733412882313e-05</v>
       </c>
       <c r="EW6" t="n">
-        <v>0</v>
+        <v>0.002194015774875879</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>0.002084180479869246</v>
       </c>
       <c r="EY6" t="n">
-        <v>0</v>
+        <v>0.004239701665937901</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>0.000480216316645965</v>
       </c>
       <c r="FA6" t="n">
-        <v>0</v>
+        <v>0.0002267158124595881</v>
       </c>
       <c r="FB6" t="n">
-        <v>0</v>
+        <v>0.001842987490817904</v>
       </c>
       <c r="FC6" t="n">
-        <v>0</v>
+        <v>0.002641804981976748</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>0.001927850302308798</v>
       </c>
       <c r="FE6" t="n">
-        <v>0</v>
+        <v>0.001161912921816111</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>0.0002403245744062588</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>0.0006815569940954447</v>
       </c>
       <c r="FH6" t="n">
-        <v>0</v>
+        <v>0.005052804946899414</v>
       </c>
       <c r="FI6" t="n">
-        <v>0</v>
+        <v>0.002247478114441037</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0</v>
+        <v>0.001641387585550547</v>
       </c>
       <c r="FK6" t="n">
-        <v>0</v>
+        <v>0.0005591054214164615</v>
       </c>
       <c r="FL6" t="n">
-        <v>0</v>
+        <v>0.004861208610236645</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>0.001737309154123068</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>0.005582320969551802</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>0.003151589771732688</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>0.001795429503545165</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0</v>
+        <v>0.001077329041436315</v>
       </c>
       <c r="FR6" t="n">
-        <v>0</v>
+        <v>0.007438304834067822</v>
       </c>
       <c r="FS6" t="n">
-        <v>0</v>
+        <v>0.003696161555126309</v>
       </c>
       <c r="FT6" t="n">
-        <v>0</v>
+        <v>0.0001331217063125223</v>
       </c>
       <c r="FU6" t="n">
-        <v>0</v>
+        <v>0.001788489054888487</v>
       </c>
       <c r="FV6" t="n">
-        <v>0</v>
+        <v>0.0007111628074198961</v>
       </c>
       <c r="FW6" t="n">
-        <v>0</v>
+        <v>0.004438972566276789</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>0.003287127939984202</v>
       </c>
       <c r="FY6" t="n">
-        <v>0</v>
+        <v>0.002879614010453224</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0</v>
+        <v>0.002033801516517997</v>
       </c>
       <c r="GA6" t="n">
-        <v>0</v>
+        <v>0.001745986985042691</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>0.001096161431632936</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>0.004534650593996048</v>
       </c>
       <c r="GD6" t="n">
-        <v>0</v>
+        <v>0.003785070963203907</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>0.0006057890714146197</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>0.003147283103317022</v>
       </c>
       <c r="GG6" t="n">
-        <v>0</v>
+        <v>0.00387684116140008</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.2392331957817078</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3367213606834412</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.04663501679897308</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.07035785168409348</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07897709310054779</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1487060040235519</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.06192328035831451</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1798728704452515</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.04491106048226357</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2911058068275452</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2319480031728745</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.007703747600317001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2300703525543213</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2848486304283142</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1392081826925278</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1232762709259987</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1359454244375229</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.156203955411911</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.02597448974847794</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.02461747266352177</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.07382816821336746</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.08316215127706528</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.04185793548822403</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.0219946950674057</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.0003699986264109612</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.1019104793667793</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.04145233705639839</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.0873960554599762</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.07376757264137268</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.009607874788343906</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.02385160885751247</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.07107721269130707</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.04011469334363937</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.01654350943863392</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.009604849852621555</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.06192789971828461</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.04467188939452171</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1600338667631149</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.1051887348294258</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.07274581491947174</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.06892368942499161</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.01560121402144432</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.002225182950496674</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.05060915648937225</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.04732892662286758</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.1644715368747711</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.06673972308635712</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.07231332361698151</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.06028258800506592</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.2295331656932831</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.03123384341597557</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.01791159808635712</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.00931281317025423</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.02958721853792667</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.05974927544593811</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.1209397614002228</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.02507074177265167</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0.004352841526269913</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0.01206955127418041</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.1685152500867844</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.0005287365056574345</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.04364375025033951</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.07763257622718811</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.03653471916913986</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.05264780670404434</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.02353929728269577</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.02005646750330925</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.0567428320646286</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0.1021668910980225</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.03517580777406693</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.04857134073972702</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0.00242193229496479</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0.07475430518388748</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.1116982698440552</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0.07282117009162903</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0.1463394016027451</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0.06710746884346008</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.03633036091923714</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.01941033825278282</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0.06039436906576157</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.05607130751013756</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.06501422822475433</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.09421785920858383</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.04403668642044067</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.0511641688644886</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.0140350628644228</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.03618721663951874</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0.02705922722816467</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.05425358191132545</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0.02129185944795609</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0.05815746635198593</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0.04900607094168663</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0.1055049002170563</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.2171237617731094</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.06305596977472305</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0.1131682395935059</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0.009238163009285927</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0.003554292488843203</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0.0292891338467598</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0.0708165243268013</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0.08135838061571121</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0.03026945143938065</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0.04854703694581985</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0.007970434613525867</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0.04001273214817047</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0.03966967016458511</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0.07144983857870102</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0.0255675632506609</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.02061635069549084</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0.04627314954996109</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0.01683181151747704</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.03997395187616348</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0.1544024646282196</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0.07280166447162628</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0.05506875738501549</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.07408088445663452</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0.132213369011879</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.04780545458197594</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0.06958643347024918</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0.01224445179104805</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0.04639741033315659</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0.05664373189210892</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0.1251225620508194</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0.05330326408147812</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0.1125470399856567</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0.005499690305441618</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0.04797495901584625</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0.007174147292971611</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0.09386140108108521</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0.09653586149215698</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0.2276383340358734</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0.1657479554414749</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0.08919022232294083</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0.04201339185237885</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0.07003605365753174</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0.02498246729373932</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0.004522922448813915</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0.1024071201682091</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0.001259423792362213</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0.02153812535107136</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0.03481706976890564</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0.01200750283896923</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0.02185104601085186</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0.05444153398275375</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0.09941045939922333</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0.09270783513784409</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0.1106438934803009</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0.009614374488592148</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0.043072409927845</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0.0515688993036747</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0.02087101526558399</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0.08945432305335999</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0.1193149909377098</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0.08817462623119354</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0.09233905375003815</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0.03338728100061417</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0.06328336149454117</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0.012328433804214</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0.01481393352150917</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0.02675697207450867</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0.08348137140274048</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0.008188996464014053</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0.02726797759532928</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0.09974448382854462</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0.004954900592565536</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0.05504270642995834</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0.1077197566628456</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0.02653341740369797</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0.06996215134859085</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0.1603245288133621</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0.03553962707519531</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0.1360888928174973</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0.1986402422189713</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0.1712232083082199</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0.1782975345849991</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0.1685777604579926</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0.03879693150520325</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0.1170797497034073</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0.008240960538387299</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0.06952881067991257</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0.1032154932618141</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0.05129432678222656</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0.07090826332569122</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0.01658928021788597</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0.06179384887218475</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0.0003737304359674454</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0.0170655082911253</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0.06220611929893494</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0.1403784453868866</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.02461172081530094</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4570435285568237</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1462582349777222</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.05415203422307968</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.08171994984149933</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4029518663883209</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0659712478518486</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2859836220741272</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01734959334135056</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.05113227665424347</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5344600677490234</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.1602390110492706</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1296606808900833</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2208897769451141</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.3727887570858002</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.04246757924556732</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1107235476374626</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1015385687351227</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.01361287012696266</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1016159206628799</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.02613385021686554</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.122795894742012</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.06941593438386917</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.03663915395736694</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.02383529022336006</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.03887715563178062</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.05100053548812866</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.04023422300815582</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.01406723819673061</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.08279304206371307</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.006782396696507931</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.202772781252861</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.06834506988525391</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.03490900620818138</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2337889522314072</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.00153375999070704</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.02107351645827293</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1248412728309631</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.006911603268235922</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.08106356859207153</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.0134302768856287</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.06265616416931152</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.02503179758787155</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.1365559995174408</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.009004749357700348</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.02850322425365448</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.6129727363586426</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.134657621383667</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.00851927325129509</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.08717404305934906</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.2138112187385559</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.0561237558722496</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.08243628591299057</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.111136257648468</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.003174944780766964</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.1313804239034653</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.05333168059587479</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.007251985371112823</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.1428253799676895</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.04548405110836029</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.09405820071697235</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.02365353144705296</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.03545947000384331</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.01516271382570267</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.1006900370121002</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.03236585855484009</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.04960886016488075</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.122826874256134</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.1202332526445389</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.0455227792263031</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.06344100087881088</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0.0386212095618248</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.04769700020551682</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.4780646562576294</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.006279905792325735</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0.1972652971744537</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0.008000443689525127</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.1620422601699829</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.05162785947322845</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0.0199256855994463</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.003092136234045029</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0.02986731380224228</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.1354263573884964</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.01474264543503523</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.03418321162462234</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.02352895960211754</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.1047769710421562</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.001855360344052315</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.04652269929647446</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0.006788025610148907</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0.07683522254228592</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.2384622097015381</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0.01829072460532188</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.1710313111543655</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.1704511344432831</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.01873990707099438</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0.00333308195695281</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0.1218035891652107</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0.001051361672580242</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0.005985339172184467</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0.1223317533731461</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0.03532899171113968</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0.04540269076824188</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0.04454784840345383</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.099388487637043</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0.01777883991599083</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0.03545645996928215</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0.00152796134352684</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.03285399824380875</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0.2365979254245758</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0.02655714750289917</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0.1017348170280457</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.1315216720104218</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.1895710974931717</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0.01867583580315113</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.1545823067426682</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0.1225062906742096</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0.04297462478280067</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0.0730089545249939</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0.04256130009889603</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0.1196547374129295</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.06123447045683861</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.05164822936058044</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0.007746460381895304</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0.08988843858242035</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0.001797356177121401</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0.0666879415512085</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0.02488396689295769</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0.1219826489686966</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0.01098785363137722</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.1386644244194031</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0.0431821271777153</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0.02077313885092735</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0.03252645209431648</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0.1642716526985168</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0.01903149299323559</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0.07496194541454315</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0.04848659783601761</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0.1156577542424202</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0.005930871237069368</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.04087638109922409</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0.0104116965085268</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>2.692453563213348e-05</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0.01811851933598518</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0.03245657309889793</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0.1057655736804008</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0.0001072445884346962</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0.01266091503202915</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0.1510709822177887</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.1829081922769547</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0.0457654595375061</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0.01767924055457115</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0.006494281813502312</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0.01026783417910337</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0.1604245156049728</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0.02447685413062572</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0.04628277942538261</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0.03001915104687214</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.1023725122213364</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0.00908769853413105</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0.02521489188075066</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0.02873089164495468</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0.02376949042081833</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0.1435570418834686</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0.09130190312862396</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0.1162466555833817</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.0296894945204258</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.08626750856637955</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0.0531766414642334</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0.2217020988464355</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0.1032393798232079</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0.06577356904745102</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.09460492432117462</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0.01627285405993462</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0.1676681339740753</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0.02857502177357674</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0.09500572830438614</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0.1414211541414261</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0.2207769602537155</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0.0205159168690443</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0.08481448888778687</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0.05161594599485397</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0.1219001263380051</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0.008819085545837879</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0.02666276507079601</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.05963007733225822</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0.02718907408416271</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0.09825251251459122</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0.03639744967222214</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.07211775332689285</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.6680436134338379</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.03408369049429893</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3642227351665497</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3106423914432526</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2889256477355957</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05994619056582451</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3335781693458557</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01659306511282921</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.08811324834823608</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.5380793213844299</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1118043884634972</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.6132804751396179</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4423821568489075</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1807051599025726</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1749871075153351</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2883563935756683</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.04993532225489616</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.01171657163649797</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.01770437508821487</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.01613658852875233</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1192091703414917</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.08891326934099197</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.04367366433143616</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.03833156079053879</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.03494095057249069</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.1561183333396912</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.110561341047287</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.1627486646175385</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.03750455379486084</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.03773526847362518</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.07252250611782074</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.08519649505615234</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.03112348727881908</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.06623672693967819</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.04543082043528557</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.00451776385307312</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.2297259718179703</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.1546704024076462</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.03246365487575531</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.09578725695610046</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.002255592495203018</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.04987931624054909</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.02313726022839546</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.004550223238766193</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.06898491084575653</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.2613146305084229</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.09669187664985657</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.1137023419141769</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.3316352367401123</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.1251077651977539</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.04686445370316505</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.0334714874625206</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.01253899186849594</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.06366036832332611</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.1293095052242279</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.1145459115505219</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.1454814672470093</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.0233643539249897</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.1855097115039825</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.05483753234148026</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.1673833131790161</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.008066598325967789</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.0462736189365387</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.03242300450801849</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.004289999138563871</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.005558609962463379</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.03204856812953949</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.1062611490488052</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.06575937569141388</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.02051994204521179</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.05711544305086136</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.03703867271542549</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.1435228139162064</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.09168855845928192</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.163229689002037</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.1372605562210083</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.06374882906675339</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.01773496344685555</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.02063627913594246</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.07057754695415497</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.03799089789390564</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.2090509384870529</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.0007293941453099251</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.09805841743946075</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.01802779361605644</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.08790247887372971</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.005410915240645409</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.06753601133823395</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.03611880913376808</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.07374957203865051</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.1703165471553802</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.2720595598220825</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.2635856568813324</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.04693125933408737</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.1879158169031143</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.0540555939078331</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0.08660217374563217</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0.06374380737543106</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0.03292063251137733</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.1999060809612274</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.01650954037904739</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.1029386147856712</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.05201729759573936</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.09867755323648453</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.02311160787940025</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0.08095042407512665</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0.02089298889040947</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.07503770291805267</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.09535586088895798</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0.06118471175432205</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.1120302528142929</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.04198154434561729</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.2120687514543533</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0.1537473052740097</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.1343910843133926</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0.09903591871261597</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.04166647419333458</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.1069897413253784</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0.003575754351913929</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.04522459954023361</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.01659604720771313</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.1257593631744385</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.02069399133324623</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0.1203495040535927</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0.1193854063749313</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.02315630950033665</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.04255634546279907</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0.2047731578350067</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.1781047880649567</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.2199347466230392</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.2963191270828247</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0.07125737518072128</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0.1400416493415833</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.06222303211688995</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.1688186228275299</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.1391245573759079</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.1393057703971863</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.05962797999382019</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.02212981134653091</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.090340256690979</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0.02256343513727188</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0.0630774199962616</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0.06038438528776169</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0.05799437314271927</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.2234576046466827</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0.07854240387678146</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.000775105319917202</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.1506501436233521</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.02628383040428162</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0.01400658302009106</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.1579598486423492</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0.05999261513352394</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0.02622391656041145</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.234315350651741</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0.006653910037130117</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.1371365040540695</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.03300349786877632</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.06407013535499573</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0.007567437365651131</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0.1164586693048477</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0.0009072148241102695</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.03637588396668434</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.08837403357028961</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0.01763531193137169</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.06673122942447662</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.1416152119636536</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.03080851398408413</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0.04117866232991219</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0.101656898856163</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0.006359631195664406</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0.1121636629104614</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.3708672821521759</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0.2371993362903595</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.2594590783119202</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.06860744953155518</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.1652843058109283</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0.1388333588838577</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0.08310932666063309</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0.1234745532274246</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0.00246657058596611</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.04791174083948135</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0.04018992185592651</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.09543284028768539</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0.06036572158336639</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.04333910718560219</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0.02014880999922752</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0.1359095871448517</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0.02156372554600239</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3.447404139933496e-09</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5.842598627125994e-10</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.110694063972574e-09</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.290053118831793e-09</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.343529731911985e-09</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.440009083670702e-09</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.041831287906803e-09</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.821301331972336e-09</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.001637383093225e-09</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.881036881812292e-09</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.803842408776291e-09</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.233547290510842e-09</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.969152949703016e-10</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.087459342689726e-09</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.109431213563994e-09</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.260508085745073e-09</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.826095719081877e-09</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5.136381098225229e-09</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.621238032711858e-09</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.600084842401372e-09</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8.807548579348179e-10</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.070610598068015e-10</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.275287263626581e-10</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.084684356222887e-10</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.715095701714802e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.492403423064559e-10</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.132296922889964e-09</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.761601169964933e-09</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.636111773313132e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.883057792502086e-09</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.014023753853621e-09</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.299699541907785e-09</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5.889809751025155e-10</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.955079431681384e-09</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7.364419074562534e-10</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.168781876836889e-10</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.601575621596908e-09</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>9.333391837174076e-10</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>6.321855261504084e-10</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.778917291250792e-10</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.853431713134569e-09</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.592150407300437e-10</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.390176029847368e-10</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>5.437951200448765e-10</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.022340989642601e-09</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.914955305437616e-09</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.100104060242529e-09</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.683779558118829e-10</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.140218586215269e-09</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.931765941127651e-09</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.641637880136273e-09</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>8.982696253490019e-10</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.743821139882812e-10</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.174974673112672e-09</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.468751786859457e-09</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.532196840045799e-09</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.193947163358189e-10</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.356405014505071e-09</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.298190970861924e-09</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.908628976034834e-09</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.563855267505687e-09</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.166143070996384e-09</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.624200466984973e-10</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>5.669150704434855e-10</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.66782121446829e-09</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.591454967808659e-09</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>2.221534067814446e-11</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>9.373162246362199e-10</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2.099546758671522e-09</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>2.091252060409943e-09</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.147929529210501e-10</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1.165944008008069e-09</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.145670225355389e-09</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1.486019529650662e-09</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>5.8318461171325e-10</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1.229718993300821e-09</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>3.051204622295245e-09</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>4.817841681159507e-10</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>8.335905299361457e-10</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>1.811431116216511e-09</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>2.079968419721467e-09</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>9.004608725327046e-10</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>8.297116327327103e-10</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>5.398714253423975e-10</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>2.686079969560495e-10</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>1.050408537928149e-09</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>4.557849098141276e-10</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>6.480183056822852e-10</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>2.525565173661093e-11</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>2.119583258908264e-10</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.265200471640583e-09</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>4.602096481676199e-10</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>5.510677469899861e-10</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>9.043532589458891e-11</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>5.932766722338556e-09</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>7.750219355173726e-10</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>9.646232701499002e-10</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>4.660754560070757e-10</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.067714472391401e-09</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>8.076916913068999e-10</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1.359576756732039e-10</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>8.06715472201347e-10</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>8.942083185026206e-11</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>1.047913977814119e-09</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>2.382914143783665e-10</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>3.806900905622967e-10</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>3.709870466384046e-10</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>4.758958782602463e-10</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>2.417058997394861e-09</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>9.204786932670572e-10</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>1.624721024384712e-09</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>6.177305333920913e-10</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>1.938891935893139e-09</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>2.216090644324709e-09</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>2.293697898281266e-09</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>3.210541610343398e-09</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>3.897039135836167e-09</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>2.477123395294711e-09</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>2.475530891388189e-09</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>2.162503509595126e-10</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>1.895349210911945e-09</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>5.500087052467961e-10</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>3.269150949947175e-09</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>5.052946949746229e-11</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>9.453057225883299e-10</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>1.286546313927772e-09</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>9.616545337820526e-10</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>6.209215364094689e-10</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>2.470241788898875e-10</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>2.072936045038887e-09</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>4.876081760585294e-09</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>1.678347016920156e-09</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>7.258605938531559e-10</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>5.062521513110596e-10</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>3.197345443961552e-10</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>1.367305824118148e-09</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>2.950268029877634e-09</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>9.379381715746149e-10</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>9.374672149675689e-10</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>8.842288568011725e-10</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>5.681763948217622e-10</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>3.270321791148945e-10</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>1.798600934854733e-09</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>5.37510036480171e-10</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>3.104807522191777e-10</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>9.541452072880929e-10</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>1.44672929192069e-09</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>4.115894292056055e-10</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>1.143637184952695e-09</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>1.515883307767751e-09</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>1.758442502719504e-09</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>7.238826205124838e-10</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>1.023643170228183e-09</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>1.22462973095594e-09</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>4.758332616816574e-10</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>5.030799665739494e-10</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>4.001981523948928e-10</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>7.299532644999829e-10</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>4.625134997215952e-10</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>5.732768149080414e-10</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>3.701597917071808e-10</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>8.227228620594218e-11</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>4.997607883083788e-10</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>9.871503614533594e-10</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>3.152145877649559e-09</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>2.364642259777838e-09</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>8.279806840150172e-10</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>4.281707766118359e-10</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>2.998951642574355e-10</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>6.004183816799014e-10</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>9.531739841861508e-10</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>5.738952868483693e-09</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>9.39892608187165e-11</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>4.885667426179907e-09</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>6.81715928152471e-09</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>1.021086770691682e-09</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>2.335490245641836e-09</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>2.839649071439965e-10</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>3.102241796781868e-09</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>8.712498777985189e-11</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>1.455882414624909e-09</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>1.573327912396394e-09</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>1.343416045074264e-09</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>2.416034594610039e-10</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>2.213729421995936e-09</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>2.625326400718109e-09</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>1.1184394521635e-09</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>1.743639566065269e-09</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>6.857174272845157e-10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.07266855239868164</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.425869345664978</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3000845909118652</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01452763378620148</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.06873659044504166</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.206745982170105</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1580829620361328</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.06696035712957382</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.994379848241806e-05</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.06630511581897736</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.4703900516033173</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3966414928436279</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1188633069396019</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.002613699994981289</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05870236456394196</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.1649671345949173</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.0004327632486820221</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.08206858485937119</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.004831276834011078</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.06318108737468719</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.1102349162101746</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.01755858771502972</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.02529524452984333</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.2230077981948853</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.05427277088165283</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.02136272005736828</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.1012119054794312</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.1573407351970673</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.05184122920036316</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.04177308827638626</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.1628983616828918</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.2119351029396057</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.2152041345834732</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.1523829847574234</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.02907893434166908</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.01661539077758789</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.1113378629088402</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.1856585443019867</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.1534977853298187</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.03846069425344467</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.1498062163591385</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.2293156981468201</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.02054223418235779</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.04098855704069138</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.06134732067584991</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.0006937719881534576</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.2238945960998535</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.1653087735176086</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.104737401008606</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.07039500027894974</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.1813727021217346</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.05644115433096886</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.01889623887836933</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.0160986352711916</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.171018585562706</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.04341762885451317</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.1343981623649597</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.02282971516251564</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.04112476110458374</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.04243949055671692</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.1765443086624146</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.1882128268480301</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.007223031483590603</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.04118989408016205</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.1104751080274582</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.05531246960163116</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.1708239316940308</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.08394719660282135</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.05839012563228607</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.1672662198543549</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.0172874927520752</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.05996208637952805</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.05876278132200241</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.1072904020547867</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0.2092342376708984</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.07908958196640015</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.0436890609562397</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.276947408914566</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.0391412228345871</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.04785798862576485</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.02179916389286518</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.02152296155691147</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.1656560003757477</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.1119014620780945</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.005872476845979691</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.05523665621876717</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.02152444422245026</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.02773887291550636</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.03058063983917236</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.02801137045025826</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.1338817477226257</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.07512173056602478</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.2952249050140381</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.1960584372282028</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.1520514339208603</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.04365148395299911</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.006373364478349686</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.01211277954280376</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.07526185363531113</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.02809076197445393</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.1612550616264343</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.1145236939191818</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.02242915332317352</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.01762853190302849</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.02097075991332531</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0.05092440918087959</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0.04794742539525032</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.007485741749405861</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.05501198023557663</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.1415752768516541</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.01132995076477528</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.04585916921496391</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.2327909767627716</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.2091471701860428</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0.08721480518579483</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.1694465726613998</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0.03702282905578613</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.02533722668886185</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.1362261921167374</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0.04769738018512726</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.01277622394263744</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.02279306203126907</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.01194656733423471</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.02017815038561821</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0.03070736117660999</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0.1117728799581528</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.01207312941551208</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.02546683326363564</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0.1667259931564331</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.06298087537288666</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.1234202980995178</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.03003828413784504</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0.02631738036870956</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0.09679137915372849</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0.1012924090027809</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.02346722595393658</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.207919254899025</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0.01713111810386181</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.03693773597478867</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.0906243771314621</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.05725548416376114</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0.03857717290520668</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.01280709356069565</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0.006775143556296825</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.023972287774086</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.1314573287963867</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0.1261237412691116</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.04642152041196823</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.08852499723434448</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.0370045006275177</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0.04238521307706833</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0.005141561385244131</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0.06227658689022064</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.02029462903738022</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.1924578249454498</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0.1012077927589417</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.01097658276557922</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.05544255673885345</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.02604949288070202</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0.03797955811023712</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0.04883041977882385</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0.0190009530633688</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.05549819394946098</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.04880477115511894</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0.04742837324738503</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.07607908546924591</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.07844569534063339</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.141490638256073</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0.01048268377780914</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0.03377575054764748</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0.04951533675193787</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0.1663835942745209</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.1595793068408966</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0.1037159562110901</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.05002016574144363</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.1886620968580246</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.2360771894454956</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0.007896937429904938</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0.04142279177904129</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0.1297703832387924</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.05513044446706772</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.1925605088472366</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0.176873967051506</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.02761126682162285</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0.09071460366249084</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.0875743180513382</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0.1242794245481491</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0.04238384962081909</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0.01974784024059772</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.0003722053079400212</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.002289273543283343</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0006561867776326835</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0004793535044882447</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.001423146110028028</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.002894565695896745</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001135227852500975</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.002062417333945632</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.0009426590986549854</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.0007307255291379988</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.00276664923876524</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.001487169764004648</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.001097304048016667</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.002757247071713209</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.003752828110009432</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0006301279063336551</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.0009106147335842252</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.0007930960855446756</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9.984989446820691e-05</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.9132428355515e-06</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.0005452627083286643</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.0003697158535942435</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.0006559666944667697</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0006745916325598955</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.0005853329785168171</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.0009123217896558344</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.0004262734728399664</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.0007916071335785091</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.000100904842838645</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.0002681128971744329</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.001012150198221207</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.0009598998003639281</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.001168774906545877</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.658717858139426e-05</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.001952522434294224</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.0001198918325826526</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.0002594683901406825</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.0001162464177468792</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.0001174807839561254</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.0003302829572930932</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.0006691076559945941</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.0003743672859854996</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.0002899341052398086</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.0009281342499889433</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.0002672586706466973</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.0001863074721768498</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.002976876916363835</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.0004185068828519434</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.0005460490938276052</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.001455667894333601</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.002226284239441156</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>7.646341691724956e-05</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.0004542957176454365</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9.466773917665705e-05</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.0002277248859172687</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.0004651796771213412</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.0005037900409661233</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.0006668178830295801</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.0006548932869918644</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>7.315819675568491e-05</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.0003081866598222405</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.002250695135444403</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.0006782853743061423</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1.304866964346729e-05</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.001191217685118318</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.0004757604619953781</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.548360160086304e-06</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.0007691968348808587</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.0003245480475015938</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.001497056917287409</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.0005410368903540075</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.000339349964633584</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.0001277332630706951</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.001282696612179279</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.0004613028140738606</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.0004480754432734102</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.0006695486372336745</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.001284015597775578</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.0003809637273661792</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.000296247802907601</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.0002570051001384854</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>5.227354995440692e-05</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.0005946236196905375</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.0001979134394787252</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.0002438975207041949</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.000641196733340621</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.0007648601313121617</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.0002864142588805407</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.0002197810390498489</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.0001888633996713907</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>3.494092379696667e-05</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.001389741897583008</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.0008238088339567184</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.001673612743616104</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.0001128476578742266</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.0003874095564242452</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>4.637209349311888e-05</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.001141155487857759</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.0003740205720532686</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0.0002161562006222084</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.0005230287788435817</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0.0002326653193449602</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.0004038363404106349</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.0005344543023966253</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.0009331696201115847</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0.0001491409202571958</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0.0001146269642049447</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>7.322891906369478e-05</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.0003314547939226031</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.001028254861012101</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.000558822532184422</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>2.986727849929594e-06</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.001222183695062995</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.001280820346437395</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0.000374491501133889</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.0005649442900903523</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>6.765806756448001e-05</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.0002080549893435091</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>4.953230381943285e-05</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0.0001090462537831627</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0.0005148554919287562</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.0002770219289232045</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.0002298481995239854</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.000457874673884362</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0.0007009427063167095</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0.0002387694257777184</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0.0002299143234267831</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.0002329472190467641</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0.0002421262615825981</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.000794727704487741</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.0001811081310734153</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>6.044216570444405e-05</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0.0001330453378614038</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0.00095494365086779</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.001543782884255052</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0.000129447435028851</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0.000384691811632365</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.0001597385125933215</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0.0001927667908603325</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.0003535135183483362</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.0009644608362577856</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0.0003753849887289107</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0.0001313662651227787</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>2.64472073467914e-05</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0.0003999127075076103</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.000516720931045711</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.0007243361324071884</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.0002462879056110978</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.0004393357958178967</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.0008341104839928448</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.0003640335635282099</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>8.09101911727339e-05</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.0004209337930660695</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0.0002643679035827518</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.0008016598294489086</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0.0001556869538035244</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.000476125831482932</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.0005209321388974786</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.0007881319615989923</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0.0002654865966178477</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>2.905119981733151e-05</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>3.651744191301987e-05</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0.0001162241460406221</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.0009145263466052711</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.0005097914254292846</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.0002451591426506639</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.0005286919767968357</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.0005768050905317068</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0.0006729608867317438</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>6.905416375957429e-05</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.001539369928650558</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>7.122183160390705e-05</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.0007938992348499596</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0.0008654525154270232</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.0007854546420276165</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.001516002928838134</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0.0002424834528937936</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0.0001954171457327902</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0.001807188498787582</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0.000299086474115029</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0.0004456306924112141</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.0006274166516959667</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.001069594523869455</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0.0001761882158461958</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0.001116673462092876</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.001288107479922473</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0.0006656418554484844</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0.0001047260884661227</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0.0005194242694415152</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.03332002833485603</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1572003662586212</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.05295044183731079</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.4008709788322449</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.07980217039585114</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2873640060424805</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1890092343091965</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1640183329582214</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05044185742735863</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.03785189613699913</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.07387929409742355</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.08345559239387512</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5714789032936096</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2551647424697876</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.3116186857223511</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.2569214105606079</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.09679181128740311</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.05732998624444008</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.02124003507196903</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.01056655403226614</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.01073366776108742</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.04626714065670967</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.08112186938524246</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.07212560623884201</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.002780089154839516</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.05685938894748688</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.005429359152913094</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.0314706414937973</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.04485982283949852</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.04191809520125389</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.002813184633851051</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.00579596683382988</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.1358684897422791</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.05596178025007248</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.1019748672842979</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.07032553851604462</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.01227591186761856</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.1190500482916832</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.03682960569858551</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.09856490790843964</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.03156458213925362</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.02266299724578857</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.08565734326839447</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.05037704855203629</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.01378689147531986</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.08573766052722931</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.09271480143070221</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.09951463341712952</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.1487984955310822</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.3021009862422943</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.1746287643909454</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.05822671949863434</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.06919169425964355</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.04567981511354446</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.01015046425163746</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.03422819077968597</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.04137925803661346</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.02416320145130157</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.1334888190031052</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.04939179867506027</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.03080589696764946</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.06373288482427597</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.06240308284759521</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.04879382997751236</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.1029543578624725</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.03502343595027924</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.1289634257555008</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.03788606449961662</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.05150587484240532</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.02599243447184563</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.004355359356850386</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0.04314160719513893</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0.007377790287137032</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.08032117784023285</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0.0202152281999588</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0.2019138932228088</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0.09085290133953094</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0.1201169863343239</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.06835988163948059</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0.02346701174974442</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.002144556026905775</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.01320854853838682</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.04130101203918457</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.0184381902217865</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.1428492069244385</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.01966448873281479</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.05516138300299644</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.01247585192322731</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.05295097082853317</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0.03444156423211098</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0.02027356252074242</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0.05421286076307297</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0.09615390002727509</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.176808089017868</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.03004070557653904</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.008962688967585564</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0.004666747525334358</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0.101243183016777</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0.03238924592733383</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0.005933486390858889</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0.0345105268061161</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0.02963387221097946</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.1510184407234192</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.05719177424907684</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.06540631502866745</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0.02103494480252266</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0.0559721365571022</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0.04667344689369202</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0.0577070415019989</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>0.1030419021844864</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0.01038060896098614</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0.1208419352769852</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.03879397362470627</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0.2205738872289658</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0.0121562946587801</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0.1392382830381393</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0.06541503220796585</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.03327494114637375</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0.07423131167888641</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0.008974275551736355</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0.01439371518790722</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0.06025649234652519</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.02653825283050537</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0.01730344630777836</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0.1084933653473854</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0.1053661331534386</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.03850404545664787</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0.03310498595237732</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0.1670485138893127</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0.1304199397563934</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0.008457627147436142</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0.06718992441892624</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0.03479332849383354</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0.1190256923437119</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0.07751011848449707</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0.08610328286886215</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>0.0003036707639694214</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0.0522637739777565</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.1141001284122467</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.01037317235022783</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0.02032443135976791</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0.00644058920443058</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0.01529622916132212</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0.04222311079502106</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0.001748645678162575</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0.07235460728406906</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0.0002762600779533386</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0.1143434345722198</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.001281566452234983</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.02276072278618813</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0.03218505904078484</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0.08358634263277054</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0.1042952761054039</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0.01472172699868679</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>0.0445527620613575</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0.008571113459765911</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0.1663757562637329</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.02936043590307236</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.05348297208547592</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0.02458085492253304</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0.05887557193636894</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0.01871851086616516</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0.0328805036842823</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.01428628526628017</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0.08784787356853485</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.07589766383171082</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0.01952375844120979</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.09113967418670654</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0.006107494235038757</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0.07390859723091125</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0.07056690752506256</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0.1443266272544861</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0.07312531769275665</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0.137632429599762</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.1639033704996109</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.01652293838560581</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0.03099238127470016</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0.1211893856525421</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0.2485111504793167</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0.01006302889436483</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0.02547743543982506</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0.07354113459587097</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0.08693351596593857</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0.1201649233698845</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0.1423700451850891</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.118370033800602</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0.05718589946627617</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0.01772717013955116</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0.01541974488645792</v>
       </c>
     </row>
   </sheetData>
